--- a/output/full_scan/batch_seq7_2026-08-27.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-27.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6517</v>
+        <v>6805</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>907.8954751416428</v>
+        <v>1089.402294915413</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>73.7</v>
+        <v>2225</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.37389203162806</v>
+        <v>69.85427607523837</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15.67814160967773</v>
+        <v>26.21430274939518</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.260685232284288</v>
+        <v>2.040229491541345</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.080178004936791</v>
+        <v>32.57840838112776</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6670</v>
+        <v>6517</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>871.2391966785069</v>
+        <v>1077.895475141643</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>277.5</v>
+        <v>73.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.23107873481467</v>
+        <v>64.37389199352209</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15.55119710841287</v>
+        <v>15.6781416793357</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.108538338705797</v>
+        <v>2.260685232284288</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.8743277443033977</v>
+        <v>1.080178004383476</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6486</v>
+        <v>6670</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>839.1303099318036</v>
+        <v>1011.239196678507</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>277.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>61.09988513887451</v>
+        <v>63.23107829591044</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21.59436613118588</v>
+        <v>15.55119708173403</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.047288595360205</v>
+        <v>3.108538338705797</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.5110154122665758</v>
+        <v>0.8743277441126157</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6805</v>
+        <v>6486</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>774.4022949154134</v>
+        <v>979.1303099318036</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2225</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>69.85427607074772</v>
+        <v>61.0998850816432</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.21430274452919</v>
+        <v>21.59436615828452</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.040229491541345</v>
+        <v>2.047288595360205</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>32.57840838303571</v>
+        <v>0.5110154121902601</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>760.1093995830026</v>
+        <v>960.1093995830026</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>520</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.10724758511364</v>
+        <v>67.10724758400745</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22.40292473852739</v>
+        <v>22.4029247319728</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.110939958300269</v>
@@ -776,17 +776,17 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>11.51724517713145</v>
+        <v>11.51724517715055</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>738.3064935784651</v>
+        <v>958.3064935784651</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>42.95</v>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>70.83747269426965</v>
+        <v>70.83747288306057</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21.71506984361956</v>
+        <v>21.71506986072363</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.322126249540955</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.6643132697711484</v>
+        <v>0.6643132691892222</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6581</v>
+        <v>6669</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>734.5394487859592</v>
+        <v>897.0176618434936</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>109.5</v>
+        <v>6815</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>60.15122824315657</v>
+        <v>68.42397666213122</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.40878862334865</v>
+        <v>27.60885436320815</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.037355469908094</v>
+        <v>0.9020946968533822</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1148969023010456</v>
+        <v>21.47294100029853</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6761</v>
+        <v>6789</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>706.456926412742</v>
+        <v>854.197356117499</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>185</v>
+        <v>462.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.18548285766771</v>
+        <v>54.32812645322421</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.39259054753856</v>
+        <v>22.53579034348843</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.2248530358362</v>
+        <v>2.579123782838694</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.042058163098111</v>
+        <v>4.689034615084879</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6789</v>
+        <v>6598</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>684.197356117499</v>
+        <v>848.1259972210829</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>462.5</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>54.32812646317028</v>
+        <v>55.57689799535938</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.53579028512608</v>
+        <v>22.53485390233022</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.579123782838694</v>
+        <v>0.6877582506317533</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>4.689034615466461</v>
+        <v>-0.16669370539451</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6530</v>
+        <v>6782</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>656.6423650420342</v>
+        <v>840.2347411119497</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>89</v>
+        <v>243.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.47637028441962</v>
+        <v>74.59795090103948</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15.13616135494807</v>
+        <v>27.04030047811034</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.122638313557953</v>
+        <v>1.62347411119497</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.975452068129482</v>
+        <v>4.403436064551411</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6716</v>
+        <v>6538</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>655.2219589637984</v>
+        <v>833.3074723591965</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>127.5</v>
+        <v>222</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.06565614555694</v>
+        <v>79.6882196067649</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.69283751284244</v>
+        <v>36.86186620200246</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8616471971193642</v>
+        <v>0.8482737872444506</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.8554937896595565</v>
+        <v>3.936593418844891</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6669</v>
+        <v>6530</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>652.0176618434936</v>
+        <v>826.6423650420339</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6815</v>
+        <v>89</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.42397665576213</v>
+        <v>59.47637029389376</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>27.60885431778753</v>
+        <v>15.13616141517087</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.9020946968533822</v>
+        <v>2.122638313557953</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>21.47294100316003</v>
+        <v>0.9754520678814484</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6584</v>
+        <v>6741</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>649.8108576093732</v>
+        <v>809.9308188238901</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>620</v>
+        <v>60.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.63431632734953</v>
+        <v>67.92018690268419</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.9512860056738</v>
+        <v>25.57722502840134</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9507970888498428</v>
+        <v>1.419104705563044</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>9.746869125972982</v>
+        <v>0.6834645646611328</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6782</v>
+        <v>6829</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>640.2347411119497</v>
+        <v>805.7644737432519</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>243.5</v>
+        <v>240.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>74.5979508944436</v>
+        <v>62.28116803821599</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.04030044521328</v>
+        <v>16.99609183759101</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.62347411119497</v>
+        <v>2.274747082028802</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>4.403436065219192</v>
+        <v>3.135076360665819</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6741</v>
+        <v>6658</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>639.9308188238901</v>
+        <v>794.6410192771772</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>60.4</v>
+        <v>171</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>67.92018689461176</v>
+        <v>56.34541483191216</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.57722507854763</v>
+        <v>11.74966098192308</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.419104705563044</v>
+        <v>1.433423675669475</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.683464564813773</v>
+        <v>1.8111858894475</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6598</v>
+        <v>6584</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>638.1259972210829</v>
+        <v>789.8108576093724</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>29</v>
+        <v>620</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.57689795957877</v>
+        <v>60.63431624512184</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.53485381381902</v>
+        <v>25.95128593947585</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6877582506317533</v>
+        <v>0.9507970888498428</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1666937053372735</v>
+        <v>9.746869127308347</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6538</v>
+        <v>6781</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>633.3074723591965</v>
+        <v>776.2623130059799</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>222</v>
+        <v>1140</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>79.68821960797285</v>
+        <v>57.94279773685964</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.86186620089453</v>
+        <v>13.24837465253603</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8482737872444506</v>
+        <v>1.343353976215844</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>3.936593419092926</v>
+        <v>1.50665058478813</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6498</v>
+        <v>6830</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>628.9675729965375</v>
+        <v>769.6061100376224</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>78.7</v>
+        <v>530</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.49200881231155</v>
+        <v>66.3464471105315</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.81537858377976</v>
+        <v>23.04047408617906</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.505617733482685</v>
+        <v>1.421857114624514</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.8990203772195358</v>
+        <v>15.48620077624095</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6532</v>
+        <v>6651</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>618.9887037389103</v>
+        <v>763.8531251899517</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>150.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.5775143946627</v>
+        <v>64.21474563551143</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32.07607984995173</v>
+        <v>24.7152991168281</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.021837568317313</v>
+        <v>1.09468043138016</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.8923451111312986</v>
+        <v>2.010976257123585</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6829</v>
+        <v>6588</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>605.7644737432519</v>
+        <v>758.8022512302658</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>240.5</v>
+        <v>110.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.28116804181482</v>
+        <v>62.45359454474305</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>16.99609179842898</v>
+        <v>25.15079796586344</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.274747082028802</v>
+        <v>0.9802251230265814</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>3.135076360952005</v>
+        <v>2.162577597605177</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6505</v>
+        <v>6581</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>600.6749197345503</v>
+        <v>754.5394487859594</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>72.7</v>
+        <v>109.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>53.36826125017426</v>
+        <v>60.15122813128921</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26.52160056581825</v>
+        <v>22.40878872398279</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7526979253462081</v>
+        <v>3.037355469908094</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.2291918300501916</v>
+        <v>0.1148969022056566</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6651</v>
+        <v>6498</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>593.8531251899515</v>
+        <v>743.9675729965375</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>150.5</v>
+        <v>78.7</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.21474564063325</v>
+        <v>52.49200890772742</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.71529910539183</v>
+        <v>23.81537873997735</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.09468043138016</v>
+        <v>1.505617733482685</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.01097625729529</v>
+        <v>0.8990203764563498</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6588</v>
+        <v>6532</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>588.8022512302658</v>
+        <v>733.9887037389105</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>110.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.45359453222032</v>
+        <v>64.57751436637943</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.15079796586344</v>
+        <v>32.07608007524332</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9802251230265814</v>
+        <v>1.021837568317313</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.162577597691037</v>
+        <v>0.8923451118181474</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6491</v>
+        <v>6761</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>575.9943675380212</v>
+        <v>706.4569264127418</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>375</v>
+        <v>185</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.89250051450589</v>
+        <v>59.18548285506387</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.40764003043299</v>
+        <v>21.39259056663105</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4489830474869761</v>
+        <v>1.2248530358362</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.3383928066487129</v>
+        <v>2.042058162869171</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6577</v>
+        <v>6640</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>569.608515618751</v>
+        <v>692.1673315668669</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>80.3</v>
+        <v>1075</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>50.4333042727803</v>
+        <v>57.05549184092532</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.22843169782194</v>
+        <v>17.22205716437415</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4182031982217624</v>
+        <v>1.739417647643397</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0505464994692013</v>
+        <v>9.519275081383949</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6605</v>
+        <v>6491</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>562.5275624785869</v>
+        <v>685.9943675380213</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>142</v>
+        <v>375</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.66571279903761</v>
+        <v>57.89250052450656</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14.22262692921185</v>
+        <v>24.40764013921717</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.171721074873692</v>
+        <v>0.4489830474869761</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.2576720133236387</v>
+        <v>-0.3383928076981233</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6781</v>
+        <v>6666</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>561.2623130059799</v>
+        <v>679.2031863637542</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1140</v>
+        <v>44.35</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.94279764246136</v>
+        <v>55.59540963270765</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13.24837460060059</v>
+        <v>20.40647704213476</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.343353976215844</v>
+        <v>0.6046244419950113</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,11 +1948,11 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.506650598143777</v>
+        <v>0.1635263468119906</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>558.1736215173455</v>
+        <v>673.1736215173455</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>43.3</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.10373878603608</v>
+        <v>49.10373881508494</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>19.72006018016593</v>
+        <v>19.72006019432681</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.672473896131603</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.662061099305427</v>
+        <v>0.6620610990860083</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6672</v>
+        <v>6605</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>547.0162276904084</v>
+        <v>672.5275624785868</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>281.5</v>
+        <v>142</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.82196265919437</v>
+        <v>59.66571300637784</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>19.94524671500315</v>
+        <v>14.22262693123793</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7769436080294925</v>
+        <v>1.171721074873692</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.981019462392444</v>
+        <v>0.2576720125604628</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6796</v>
+        <v>6533</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>546.9104820105897</v>
+        <v>662.794259875351</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>62.5</v>
+        <v>268.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.39688079232708</v>
+        <v>67.75833214213579</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.97778022354879</v>
+        <v>15.12165701205645</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7316485703600879</v>
+        <v>0.9860511027341584</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.314640480776347</v>
+        <v>1.339273159544936</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6666</v>
+        <v>6716</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>539.2031863637542</v>
+        <v>655.2219589637984</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>44.35</v>
+        <v>127.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.59540944473714</v>
+        <v>65.06565612770723</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.40647697692212</v>
+        <v>34.69283753492999</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6046244419950113</v>
+        <v>0.8616471971193642</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1635263470791</v>
+        <v>0.8554937898503567</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6753</v>
+        <v>6642</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>532.2083901955281</v>
+        <v>640.2539179562639</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>144.5</v>
+        <v>82.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.72265878271244</v>
+        <v>55.87769735558752</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.61965751023396</v>
+        <v>15.20726353387519</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.046114165300614</v>
+        <v>0.7120492900865663</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0030785227504117</v>
+        <v>-0.1873892109309442</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6771</v>
+        <v>6672</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>531.0655924401561</v>
+        <v>637.0162276904083</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>41.75</v>
+        <v>281.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.1660267035318</v>
+        <v>59.8219626656855</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>41.8969555165968</v>
+        <v>19.9452468019823</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.816319780678141</v>
+        <v>0.7769436080294925</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,51 +2266,51 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2459431898858368</v>
+        <v>1.981019462125328</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6806</v>
+        <v>6739</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>633.8721903301165</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>3.51</v>
+        <v>1095</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>31.69502516306633</v>
+        <v>56.57482044388591</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.59319902426274</v>
+        <v>8.779937463421954</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.476038399100268</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4112821382566496</v>
+        <v>10.38816298408951</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6642</v>
+        <v>6515</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>500.2539179562639</v>
+        <v>626.9984411308145</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>82.2</v>
+        <v>6105</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.87769735109595</v>
+        <v>40.70041989270533</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.2072634646164</v>
+        <v>16.59684646210167</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7120492900865663</v>
+        <v>1.426858004568525</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1873892109309442</v>
+        <v>-1.983449778533242</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6640</v>
+        <v>6548</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>492.1673315668668</v>
+        <v>602.4887217754771</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1075</v>
+        <v>75</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.05549186517253</v>
+        <v>54.41643856536921</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.2220572105129</v>
+        <v>12.20030005761731</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.739417647643397</v>
+        <v>1.172785890474908</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>9.519275073179784</v>
+        <v>0.4588414485464901</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6658</v>
+        <v>6706</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>484.6410192771773</v>
+        <v>602.1586851222305</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.34541487455717</v>
+        <v>54.33708474153611</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11.74966094092763</v>
+        <v>14.83891034737996</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.433423675669475</v>
+        <v>1.695003353947115</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.811185889771857</v>
+        <v>2.024194371889118</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6585</v>
+        <v>6788</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>483.9715106986736</v>
+        <v>601.7767543465361</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.68512041640778</v>
+        <v>54.52323925431228</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.76386617671185</v>
+        <v>23.24170728478405</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2716165284659114</v>
+        <v>1.115829661086629</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0228158256828805</v>
+        <v>3.173392215930549</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6533</v>
+        <v>6505</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>482.7942598753512</v>
+        <v>600.6749197345503</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>268.5</v>
+        <v>72.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>67.75833212559445</v>
+        <v>53.36826126441741</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15.12165692793296</v>
+        <v>26.52160066143995</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9860511027341584</v>
+        <v>0.7526979253462081</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.339273160975907</v>
+        <v>-0.2291918302123691</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6589</v>
+        <v>6743</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>477.8568943976867</v>
+        <v>591.8030699615041</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>50.2</v>
+        <v>27.45</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.11820434266202</v>
+        <v>52.27487951716817</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.38689152482699</v>
+        <v>23.09882305333278</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4983092153684755</v>
+        <v>1.19299502432274</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0529453314196796</v>
+        <v>0.2285753637002248</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6739</v>
+        <v>6531</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>463.8721903301159</v>
+        <v>575.0141397326764</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1095</v>
+        <v>917</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.57482039691614</v>
+        <v>54.71418165417042</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>8.779937484358106</v>
+        <v>9.2050977651522</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.476038399100268</v>
+        <v>1.179313557796266</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>10.38816298580663</v>
+        <v>8.33246891622772</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6548</v>
+        <v>6643</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>462.488721775477</v>
+        <v>573.1081669455825</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>75</v>
+        <v>442.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.41643854485172</v>
+        <v>54.26378670074898</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12.20029999685309</v>
+        <v>13.64101772732803</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.172785890474908</v>
+        <v>0.8470205339862878</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.458841448670502</v>
+        <v>2.430026572499369</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6706</v>
+        <v>6577</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>462.1586851222305</v>
+        <v>569.608515618751</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>124</v>
+        <v>80.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.33708472566889</v>
+        <v>50.4333043553683</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.83891030511988</v>
+        <v>24.2284318154187</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.695003353947115</v>
+        <v>0.4182031982217624</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>2.024194372289779</v>
+        <v>-0.0505464998317092</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6788</v>
+        <v>6625</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>461.7767543465362</v>
+        <v>561.6580566949195</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>367</v>
+        <v>77.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.52323930388884</v>
+        <v>55.23332611731467</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>23.24170728478405</v>
+        <v>10.44449694097879</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.115829661086629</v>
+        <v>0.5613919660161195</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>3.173392216121356</v>
+        <v>0.1219172432391469</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6830</v>
+        <v>6753</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>454.6061100376221</v>
+        <v>552.2083901955281</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>530</v>
+        <v>144.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>66.34644710443979</v>
+        <v>53.72265881857583</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.04047399514616</v>
+        <v>25.6196575537362</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.421857114624514</v>
+        <v>2.046114165300614</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>15.48620077681339</v>
+        <v>-0.0030785230556849</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6625</v>
+        <v>6796</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>451.6580566949194</v>
+        <v>546.9104820105897</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>77.8</v>
+        <v>62.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.23332656407696</v>
+        <v>58.39688078704186</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10.44449694047979</v>
+        <v>28.97778022399597</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5613919660161195</v>
+        <v>0.7316485703600879</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1219172422851754</v>
+        <v>0.3146404805855504</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6515</v>
+        <v>6613</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>431.9984411308147</v>
+        <v>546.8538088391224</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>6105</v>
+        <v>266</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.70041990997061</v>
+        <v>45.48587915039239</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.59684646210167</v>
+        <v>10.63517003293451</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.426858004568525</v>
+        <v>1.629834347115538</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.983449782348515</v>
+        <v>1.523044417550148</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6655</v>
+        <v>6770</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>427.6193585110554</v>
+        <v>545.3645004047846</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>117</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.62005578222316</v>
+        <v>51.99438012898021</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10.12787080662502</v>
+        <v>12.92946547408568</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4291983647542302</v>
+        <v>0.5173993378291476</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0427606077220631</v>
+        <v>0.1969084439369877</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6488</v>
+        <v>6655</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>422.3265022854824</v>
+        <v>537.6193585110552</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>958</v>
+        <v>117</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.38732031391058</v>
+        <v>49.62005187339201</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11.84682576111215</v>
+        <v>10.12787081339611</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6813136964572095</v>
+        <v>0.4291983647542302</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>6.521324219895998</v>
+        <v>0.0427606080082467</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6834</v>
+        <v>6771</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>421.3683365953621</v>
+        <v>531.0655924401561</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>41.75</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.21717383419823</v>
+        <v>58.1660267035318</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>12.06813870069192</v>
+        <v>41.8969555481091</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.67466139198594</v>
+        <v>0.816319780678141</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.5556941789510224</v>
+        <v>0.245943189714126</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6510</v>
+        <v>6526</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>420.5686322722076</v>
+        <v>529.6589319513259</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2740</v>
+        <v>610</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,66 +3202,66 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.31529710980674</v>
+        <v>53.53639757112503</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12.61107904235565</v>
+        <v>14.64917229974226</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7590064637837222</v>
+        <v>0.9980966232942636</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.557233252329361</v>
+        <v>1.761526199172715</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6770</v>
+        <v>6806</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>420.3645004047846</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>3.51</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.99438013608875</v>
+        <v>31.69502661425305</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.92946539712317</v>
+        <v>32.59319880613012</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5173993378291476</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1969084439369877</v>
+        <v>0.4112821212078614</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6693</v>
+        <v>6585</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>408.6020293560798</v>
+        <v>503.9715106986736</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.42051250573608</v>
+        <v>47.68512047533542</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.10889023669874</v>
+        <v>16.76386620218085</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6097974082908409</v>
+        <v>0.2716165284659114</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.101058398892178</v>
+        <v>0.0228158250151104</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6613</v>
+        <v>6589</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>406.8538088391224</v>
+        <v>497.8568943976867</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>266</v>
+        <v>50.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.48587914477519</v>
+        <v>54.11820438051191</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10.6351700050799</v>
+        <v>27.38689158842264</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.629834347115538</v>
+        <v>0.4983092153684755</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.523044417931713</v>
+        <v>-0.0529453317249479</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6643</v>
+        <v>6834</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>403.1081669455826</v>
+        <v>496.3683365953621</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>442.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.26378664584676</v>
+        <v>46.21717383869574</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.6410176597475</v>
+        <v>12.06813873530829</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8470205339862878</v>
+        <v>0.67466139198594</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>2.430026576315257</v>
+        <v>-0.5556941790559533</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6763</v>
+        <v>6756</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>402.5472065540695</v>
+        <v>485.0675823449431</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>42.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46.65131703566943</v>
+        <v>53.30468797285049</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.01455857412067</v>
+        <v>11.27836978932118</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8800358383342471</v>
+        <v>0.6895392839002635</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0802734437282861</v>
+        <v>0.3043577366086371</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6582</v>
+        <v>6794</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>390.9636842901274</v>
+        <v>484.4992223329913</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>32.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>58.34705775263465</v>
+        <v>59.07768587577731</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.599686887116</v>
+        <v>22.71901807181211</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7116999820190252</v>
+        <v>0.6621239472370942</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1423823487010046</v>
+        <v>0.9992362072627748</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6692</v>
+        <v>6568</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>381.3483393082541</v>
+        <v>481.3636884952934</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.2</v>
+        <v>134.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.01203762900476</v>
+        <v>47.53892772921778</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.697601454673119</v>
+        <v>44.36625361714212</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3566771401249363</v>
+        <v>1.495778243852312</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1265778221877733</v>
+        <v>1.203937123346011</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6494</v>
+        <v>6592</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>380.1585259689435</v>
+        <v>469.447499047064</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>54.8</v>
+        <v>61.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.31730751411551</v>
+        <v>53.78435683581756</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.98962268578664</v>
+        <v>11.93405973147852</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7537241300386454</v>
+        <v>0.8697897731318893</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.3588880245450255</v>
+        <v>0.1500611466430233</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6690</v>
+        <v>6691</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>372.0011256969429</v>
+        <v>464.425043400661</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>165</v>
+        <v>625</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.61979714710239</v>
+        <v>38.20859099410447</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11.12788177209151</v>
+        <v>21.44697332580289</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6087868269760032</v>
+        <v>0.8420294196113922</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2521572183029233</v>
+        <v>-9.629645661858451</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6534</v>
+        <v>6573</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>370.7681212493703</v>
+        <v>463.1758471993191</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>92.2</v>
+        <v>17.7</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46.1609963872578</v>
+        <v>49.30447424355248</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.53337359804133</v>
+        <v>16.17228425820159</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2712910642156818</v>
+        <v>0.9662714359346198</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1999679121419654</v>
+        <v>0.2456910039792731</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6756</v>
+        <v>6742</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>370.0675823449432</v>
+        <v>457.7402773773522</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.30468795024369</v>
+        <v>49.61975060942334</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11.27836977731892</v>
+        <v>16.15881873793721</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6895392839002635</v>
+        <v>3.565032581927775</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3043577372573437</v>
+        <v>0.6325642392461295</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6674</v>
+        <v>6722</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>369.1841617663966</v>
+        <v>441.9519306243848</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>16</v>
+        <v>33.15</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.58800923117108</v>
+        <v>48.83001707832141</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>27.19243582350638</v>
+        <v>36.47166371902701</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7151040386959392</v>
+        <v>0.5509368681442793</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1871349113371145</v>
+        <v>0.1590225125637291</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6560</v>
+        <v>6683</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>368.8040827738457</v>
+        <v>437.5026478583192</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>31.55</v>
+        <v>1245</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.92363311627865</v>
+        <v>51.15391130815015</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.88878228812261</v>
+        <v>18.87972635228227</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.045897256349863</v>
+        <v>1.052534078216113</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0311470153204833</v>
+        <v>9.651187056947805</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6671</v>
+        <v>6664</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>365.2443726165869</v>
+        <v>436.5006644894778</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>23.25</v>
+        <v>355</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.76875111790972</v>
+        <v>51.1914085494649</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.0804887028784</v>
+        <v>16.5405569888592</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4950351205894792</v>
+        <v>0.758337179668959</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1561778232646715</v>
+        <v>2.718903144830763</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6531</v>
+        <v>6725</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>355.0141397326764</v>
+        <v>436.4809255989069</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>917</v>
+        <v>237.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.7141816480088</v>
+        <v>42.18004734238434</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.205097679742726</v>
+        <v>30.99475862925501</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.179313557796266</v>
+        <v>1.380888916377537</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>8.332468917563322</v>
+        <v>1.823207645722974</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6742</v>
+        <v>6485</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>352.7402773773523</v>
+        <v>427.2059462782481</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>45.3</v>
+        <v>61.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.61975056635336</v>
+        <v>44.49222457136287</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.15881860164418</v>
+        <v>21.66880937208157</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3.565032581927775</v>
+        <v>0.8270434782462295</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6325642397231168</v>
+        <v>0.5771442587934947</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6561</v>
+        <v>6488</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>349.9053119237837</v>
+        <v>422.3265022854824</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>322</v>
+        <v>958</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.59791506927455</v>
+        <v>47.38732030694738</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.73799799731242</v>
+        <v>11.84682574430156</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7207545837599189</v>
+        <v>0.6813136964572095</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1962138040173813</v>
+        <v>6.521324219800594</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6573</v>
+        <v>6510</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>348.1758471993191</v>
+        <v>420.5686322722074</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>17.7</v>
+        <v>2740</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.30447424432131</v>
+        <v>49.3152970930604</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.17228425667103</v>
+        <v>12.61107904629149</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9662714359346198</v>
+        <v>0.7590064637837222</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2456910039830893</v>
+        <v>1.5572332540467</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6606</v>
+        <v>6831</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>345.269317435231</v>
+        <v>419.5221067881572</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>26.3</v>
+        <v>593</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,49 +4209,49 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.23564273836504</v>
+        <v>45.64937637346038</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.46748944568938</v>
+        <v>17.05666026615622</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4810089757878223</v>
+        <v>0.9924807277406712</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.08376655456651599</v>
+        <v>-2.36266995187226</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6831</v>
+        <v>6645</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>344.522106788157</v>
+        <v>418.7132622336153</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>593</v>
+        <v>12.9</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.64937637590921</v>
+        <v>40.95847219779496</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.05666026615622</v>
+        <v>26.02815556621744</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9924807277406712</v>
+        <v>0.337479635614243</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-2.362669951395247</v>
+        <v>0.0223640848701923</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6568</v>
+        <v>6693</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>341.3636884952933</v>
+        <v>408.6020293560798</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>134.5</v>
+        <v>167</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.53892798310565</v>
+        <v>44.42051250079596</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>44.36625360784608</v>
+        <v>15.10889029217521</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.495778243852312</v>
+        <v>0.6097974082908409</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.203937122487449</v>
+        <v>0.1010583989684894</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6715</v>
+        <v>6546</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>340.4995077499122</v>
+        <v>405.8973753855983</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>351.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.13725859292349</v>
+        <v>55.53887727665393</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.31536583457773</v>
+        <v>18.05030021985933</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7645719110851062</v>
+        <v>0.6302665324362368</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-2.844822461839756</v>
+        <v>0.4729466302005319</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6695</v>
+        <v>6763</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>340.4793686607597</v>
+        <v>402.5472065540695</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>48.3</v>
+        <v>42.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,49 +4421,49 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.06489343089466</v>
+        <v>46.65131699922344</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.5425216894726</v>
+        <v>21.01455855384688</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6947400093543604</v>
+        <v>0.8800358383342471</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0483519251519952</v>
+        <v>0.0802734432131389</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6691</v>
+        <v>6582</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>334.4250434006611</v>
+        <v>390.9636842901274</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>625</v>
+        <v>32.7</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>38.20859099977366</v>
+        <v>58.3470576710269</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.44697323499467</v>
+        <v>20.59968693256213</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8420294196113922</v>
+        <v>0.7116999820190252</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-9.629645660427482</v>
+        <v>0.1423823485960677</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6680</v>
+        <v>6679</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>329.9426177485695</v>
+        <v>390.6697651258513</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>51.2</v>
+        <v>205.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.59954367572636</v>
+        <v>44.1881878150401</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>8.063264468585693</v>
+        <v>25.5957858134647</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3692407938677068</v>
+        <v>0.5983936685520466</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.019579520588962</v>
+        <v>1.356428456515992</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6722</v>
+        <v>6674</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>326.9519306243848</v>
+        <v>389.1841617663964</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>33.15</v>
+        <v>16</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.83001646900058</v>
+        <v>52.58800931516711</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>36.47166360568104</v>
+        <v>27.19243584965717</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5509368681442793</v>
+        <v>0.7151040386959392</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1590225125637291</v>
+        <v>0.1871349112130983</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6512</v>
+        <v>6541</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>325.5154935993359</v>
+        <v>388.195517886722</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>20.5</v>
+        <v>36.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>53.41685716276522</v>
+        <v>44.77845390219729</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10.5584918667145</v>
+        <v>11.78655761716544</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.021226836438049</v>
+        <v>0.8043566623069798</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.8719398361272669</v>
+        <v>0.0073557088349002</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6525</v>
+        <v>6692</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>324.0761753523985</v>
+        <v>381.3483393082541</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>141.5</v>
+        <v>24.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.72726600096864</v>
+        <v>52.01203764658398</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.18970267018351</v>
+        <v>9.697601478942062</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5218532886585501</v>
+        <v>0.3566771401249363</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.4429127594520103</v>
+        <v>0.1265778221400728</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6803</v>
+        <v>6494</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>322.8913332411903</v>
+        <v>380.1585259689435</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>270.5</v>
+        <v>54.8</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.51638313417481</v>
+        <v>52.31730752710445</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.37882591194161</v>
+        <v>12.98962284556552</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.9079786698863064</v>
+        <v>0.7537241300386454</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4663537974506737</v>
+        <v>0.3588880244210116</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6526</v>
+        <v>6558</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>319.658931951326</v>
+        <v>373.7229664687683</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>610</v>
+        <v>25.9</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>53.5363976018371</v>
+        <v>49.61197805043293</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.64917228441398</v>
+        <v>28.45583613455241</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9980966232942636</v>
+        <v>1.130807214277604</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.761526200126728</v>
+        <v>0.1517140173203676</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6597</v>
+        <v>6690</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>318.6747929390314</v>
+        <v>372.0011256969429</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.35223432944582</v>
+        <v>52.61979706842511</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.531207799285204</v>
+        <v>11.12788168625122</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.0036680096314833</v>
+        <v>0.6087868269760032</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.11754843531745</v>
+        <v>0.2521572176351665</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6794</v>
+        <v>6534</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>314.4992223329913</v>
+        <v>370.7681212493703</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>59.07768589303837</v>
+        <v>46.1609906032496</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>22.71901807181211</v>
+        <v>16.53337359302204</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6621239472370942</v>
+        <v>0.2712910642156818</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.9992362072055304</v>
+        <v>-0.1999679120656609</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6485</v>
+        <v>6560</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>312.2059462782482</v>
+        <v>368.8040827738457</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>61.5</v>
+        <v>31.55</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>44.49222454803002</v>
+        <v>50.92363315071132</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>21.66880936310402</v>
+        <v>22.88878248904334</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8270434782462295</v>
+        <v>1.045897256349863</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>2</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.5771442591178571</v>
+        <v>0.0311470148721142</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6743</v>
+        <v>6606</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>311.803069961504</v>
+        <v>365.2693174352312</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>27.45</v>
+        <v>26.3</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.27487948865129</v>
+        <v>53.23564276079874</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>23.09882300449738</v>
+        <v>13.46748939347622</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.19299502432274</v>
+        <v>0.4810089757878223</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2285753638433216</v>
+        <v>-0.08376655465237499</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6645</v>
+        <v>6671</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>308.7132622336153</v>
+        <v>365.2443726165869</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12.9</v>
+        <v>23.25</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>40.95847223950584</v>
+        <v>50.76875107253534</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>26.02815552863663</v>
+        <v>22.08048873405237</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.337479635614243</v>
+        <v>0.4950351205894792</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.022364084984669</v>
+        <v>0.156177823312367</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6689</v>
+        <v>6695</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>300.4639642263058</v>
+        <v>360.4793686607597</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>61.5</v>
+        <v>48.3</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.01751029266638</v>
+        <v>44.06489346916099</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.70033382744247</v>
+        <v>17.54252178682031</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5557992811692597</v>
+        <v>0.6947400093543604</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1510888530684219</v>
+        <v>0.0483519248085682</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6720</v>
+        <v>6757</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>300.1937633141281</v>
+        <v>354.1710524658652</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>134</v>
+        <v>56.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.24936463612043</v>
+        <v>49.30383746044829</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>25.44378654299823</v>
+        <v>7.663185932088824</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.621675235913796</v>
+        <v>0.5685951178793155</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0840576773365123</v>
+        <v>0.1049266986371656</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6664</v>
+        <v>6561</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>296.5006644894779</v>
+        <v>349.9053119237837</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.19140856588145</v>
+        <v>46.59791515567833</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.54055695585282</v>
+        <v>10.73799798385487</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.758337179668959</v>
+        <v>0.7207545837599189</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>2.718903145689357</v>
+        <v>0.1962138034449729</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6725</v>
+        <v>6799</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>296.480925598907</v>
+        <v>346.4862530487843</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>237.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.1800472677477</v>
+        <v>47.35172464662303</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>30.99475857976291</v>
+        <v>16.33174928844023</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.380888916377537</v>
+        <v>0.4796216050653504</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.823207647726285</v>
+        <v>0.2365269276143755</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6614</v>
+        <v>6768</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>291.9517211910335</v>
+        <v>339.3052834613746</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>36.25</v>
+        <v>64.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.42870479842354</v>
+        <v>37.10961789950538</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8.932939422911602</v>
+        <v>31.31231451071035</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6271132334833905</v>
+        <v>0.4816124631850403</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.150481695912144</v>
+        <v>0.3598367860341618</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6546</v>
+        <v>6525</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>290.8973753855983</v>
+        <v>334.0761753523985</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>141.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>55.53887722369727</v>
+        <v>48.72726599989576</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>18.05030021335236</v>
+        <v>11.18970272339761</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6302665324362368</v>
+        <v>0.5218532886585501</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.4729466307347585</v>
+        <v>0.4429127593566471</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6592</v>
+        <v>6680</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>284.447499047064</v>
+        <v>329.9426177485695</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>61.6</v>
+        <v>51.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>53.78435666706589</v>
+        <v>51.59954367279682</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.9340598485125</v>
+        <v>8.063264467372083</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8697897731318893</v>
+        <v>0.3692407938677068</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.150061146929216</v>
+        <v>1.019579520608046</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6757</v>
+        <v>6792</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>279.1710524658652</v>
+        <v>327.6438973686224</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>56.2</v>
+        <v>59</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.30383730265842</v>
+        <v>53.47833341487237</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7.663185970133807</v>
+        <v>14.30816284838743</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5685951178793155</v>
+        <v>0.8120800915063808</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1049266989424355</v>
+        <v>0.3812414448748443</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6550</v>
+        <v>6512</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>278.3878370408355</v>
+        <v>325.5154935993359</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>11.35</v>
+        <v>20.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.70495332035094</v>
+        <v>53.41685716050354</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.81191520663699</v>
+        <v>10.55849184933214</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.374606992068762</v>
+        <v>1.021226836438049</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1417466935727108</v>
+        <v>-0.8719398360986454</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6541</v>
+        <v>6715</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>278.1955178867221</v>
+        <v>325.4995077499121</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>36.9</v>
+        <v>351.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.77845399629451</v>
+        <v>43.13725859843898</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.78655761059458</v>
+        <v>14.31536584493546</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8043566623069798</v>
+        <v>0.7645719110851062</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0073557090066128</v>
+        <v>-2.84482246260285</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6667</v>
+        <v>6803</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>277.0007072689909</v>
+        <v>322.8913332411903</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>222.5</v>
+        <v>270.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.55397345995598</v>
+        <v>48.51638307476813</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>29.88194688472666</v>
+        <v>24.37882596642063</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8989973244324353</v>
+        <v>0.9079786698863064</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.7627606651619629</v>
+        <v>0.4663537973552301</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6679</v>
+        <v>6579</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>275.6697651258513</v>
+        <v>321.1598302496383</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>205.5</v>
+        <v>148</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.18818780572674</v>
+        <v>41.20942856088112</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>25.59578577080995</v>
+        <v>14.23354114874256</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5983936685520466</v>
+        <v>0.5115607109071684</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>1.356428457565347</v>
+        <v>-1.217863887410911</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6735</v>
+        <v>6597</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>270.6522243014538</v>
+        <v>318.6747929390314</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>63.5</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.52227300996705</v>
+        <v>43.35223432944582</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.69105518923064</v>
+        <v>8.531207805309602</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9911847624075544</v>
+        <v>0.0036680096314833</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.7012149379298127</v>
+        <v>-2.11754843531745</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6719</v>
+        <v>6591</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>268.6360976251275</v>
+        <v>305.3904994267889</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>194.5</v>
+        <v>42.6</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>38.60285676466643</v>
+        <v>36.75972473751418</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>24.14258029942455</v>
+        <v>31.47426254382864</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6519913441797436</v>
+        <v>0.8247672115255582</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.7503256215064926</v>
+        <v>0.0910807845169108</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6683</v>
+        <v>6689</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>267.5026478583192</v>
+        <v>300.4639642263054</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1245</v>
+        <v>61.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>51.15391129925429</v>
+        <v>49.01751037777724</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.87972626228423</v>
+        <v>14.70033378370519</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.052534078216113</v>
+        <v>0.5557992811692597</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>9.65118706047744</v>
+        <v>0.1510888525532766</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6811</v>
+        <v>6720</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>262.6454705481609</v>
+        <v>300.193763314128</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>225.5</v>
+        <v>134</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>48.02074388983496</v>
+        <v>44.24936461403403</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>11.02730126647508</v>
+        <v>25.44378656320902</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3660991328111852</v>
+        <v>1.621675235913796</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.6557258264842902</v>
+        <v>-0.0840576780042933</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6657</v>
+        <v>6614</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>252.0895244992341</v>
+        <v>291.9517211910335</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>30.4</v>
+        <v>36.25</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.81348974580664</v>
+        <v>43.42870470484628</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>26.86602180994214</v>
+        <v>8.93293939947908</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.943865127338356</v>
+        <v>0.6271132334833905</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1815523596913744</v>
+        <v>0.1504816959312274</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6807</v>
+        <v>6550</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>251.6614630828871</v>
+        <v>278.3878370408355</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>33.95</v>
+        <v>11.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.83518944818374</v>
+        <v>48.70495343366474</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.32646487795762</v>
+        <v>27.811915149898</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.180685611553038</v>
+        <v>1.374606992068762</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.558946173073199</v>
+        <v>0.1417466933914544</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6579</v>
+        <v>6667</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>246.1598302496383</v>
+        <v>277.0007072689911</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>148</v>
+        <v>222.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.20942856678371</v>
+        <v>42.55397350688073</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.23354111608759</v>
+        <v>29.8819469528904</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5115607109071684</v>
+        <v>0.8989973244324353</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.217863887124722</v>
+        <v>0.7627606637310178</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6552</v>
+        <v>6657</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>243.9540112780104</v>
+        <v>272.0895244992341</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>25.35</v>
+        <v>30.4</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>49.28584720943346</v>
+        <v>43.81348984891672</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.55548052783582</v>
+        <v>26.86602177297551</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7563922635764467</v>
+        <v>0.943865127338356</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.2714323657627747</v>
+        <v>0.1815523592907078</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6768</v>
+        <v>6807</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>239.3052834613746</v>
+        <v>271.661463082887</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>64.8</v>
+        <v>33.95</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>37.10961776732569</v>
+        <v>36.83518942843164</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>31.31231452090473</v>
+        <v>22.3264648629256</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4816124631850403</v>
+        <v>0.180685611553038</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.3598367867019396</v>
+        <v>-0.5589461731113607</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6558</v>
+        <v>6735</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>238.7229664687704</v>
+        <v>270.6522243014538</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>25.9</v>
+        <v>63.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>49.61197805516639</v>
+        <v>43.52227300523869</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>28.45583612251943</v>
+        <v>17.69105518789714</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.130807214277604</v>
+        <v>0.9911847624075544</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1517140177782752</v>
+        <v>0.7012149379584418</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6624</v>
+        <v>6719</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>232.2070925054098</v>
+        <v>268.6360976251275</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>40.95</v>
+        <v>194.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>52.54475448571279</v>
+        <v>38.60285684186113</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.044923170993886</v>
+        <v>24.14258036071316</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.032061660986409</v>
+        <v>0.6519913441797436</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.3076650097903988</v>
+        <v>0.7503256204571276</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6698</v>
+        <v>6811</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>231.6858669671592</v>
+        <v>262.6454705481609</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>32.6</v>
+        <v>225.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.57014463857</v>
+        <v>48.0207439769526</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>24.11131147161301</v>
+        <v>11.0273012788927</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5617469132741608</v>
+        <v>0.3660991328111852</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2698725502187673</v>
+        <v>-0.6557258272474468</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6792</v>
+        <v>6698</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>217.6438973686224</v>
+        <v>251.6858669671592</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>59</v>
+        <v>32.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>53.47833336203902</v>
+        <v>47.57014469061384</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.30816281966331</v>
+        <v>24.1113115382354</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8120800915063808</v>
+        <v>0.5617469132741608</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.381241445027478</v>
+        <v>0.2698725499802745</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6654</v>
+        <v>6552</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>212.8954197920625</v>
+        <v>243.9540112780104</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>168</v>
+        <v>25.35</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.32167869337307</v>
+        <v>49.28584718496776</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.22578600154829</v>
+        <v>13.55548053490907</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3520725124758122</v>
+        <v>0.7563922635764467</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.4185459872347385</v>
+        <v>0.2714323656673775</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6799</v>
+        <v>6835</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>211.4862530487843</v>
+        <v>237.4966129970478</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>30.95</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>47.35172461628376</v>
+        <v>42.86888469199438</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.33174928149517</v>
+        <v>19.41037626448146</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4796216050653504</v>
+        <v>1.348347797286834</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.2365269281104391</v>
+        <v>0.1441550739669796</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6708</v>
+        <v>6790</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>204.0106693588008</v>
+        <v>232.6837300244773</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>37.5</v>
+        <v>38.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.19936663199487</v>
+        <v>45.77112890309451</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.585321829149819</v>
+        <v>14.04817557694618</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.370911209493752</v>
+        <v>0.9379469133271756</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.4519396593136942</v>
+        <v>0.063222475083623</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6570</v>
+        <v>6624</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>197.2021075361484</v>
+        <v>232.2070925054098</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>52.8</v>
+        <v>40.95</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46.07635878382878</v>
+        <v>52.54475450250152</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>12.9534043983075</v>
+        <v>6.044923192052287</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.3875317557509689</v>
+        <v>0.032061660986409</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.4930639922902503</v>
+        <v>0.3076650096472959</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6591</v>
+        <v>6654</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>195.3904994267873</v>
+        <v>212.8954197920625</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>42.6</v>
+        <v>168</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>36.75972453262931</v>
+        <v>48.32167866594728</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>31.47426260189965</v>
+        <v>15.22578598622245</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.8247672115255582</v>
+        <v>0.3520725124758122</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.09108078482218571</v>
+        <v>-0.4185459872347385</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6776</v>
+        <v>6708</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>172.1814547923084</v>
+        <v>204.0106693588008</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>53.2</v>
+        <v>37.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.00466959346193</v>
+        <v>51.19936663264042</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.16836009628672</v>
+        <v>8.585321851528763</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4840385300760095</v>
+        <v>1.370911209493752</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0382083561528774</v>
+        <v>0.4519396593232252</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6823</v>
+        <v>6556</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>164.9406948833019</v>
+        <v>203.6685386074891</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>62.7</v>
+        <v>61.4</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45.55931774277653</v>
+        <v>45.48900050377734</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>17.13538330882944</v>
+        <v>18.22481906925286</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.382635252348718</v>
+        <v>0.2268193064760106</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0862430050059306</v>
+        <v>0.3918561346003386</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6754</v>
+        <v>6570</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>157.3041461919021</v>
+        <v>197.2021075361484</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>42</v>
+        <v>52.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>46.91933885065727</v>
+        <v>46.07635892297579</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.82459842373652</v>
+        <v>12.9534046200594</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.503731132873442</v>
+        <v>0.3875317557509689</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0921246804175658</v>
+        <v>-0.4930639925859861</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6732</v>
+        <v>6776</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>156.5099095303312</v>
+        <v>172.1814547923084</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>154</v>
+        <v>53.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.79887749162757</v>
+        <v>43.00466972023832</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>19.38344310308837</v>
+        <v>16.16836005005716</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7061578652792361</v>
+        <v>0.4840385300760095</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.8198041443007371</v>
+        <v>0.0382083558857605</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6641</v>
+        <v>6823</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>152.4127275977326</v>
+        <v>164.9406948833018</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>17.75</v>
+        <v>62.7</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.95897799379684</v>
+        <v>45.55931773782235</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>8.460811888509744</v>
+        <v>17.13538330142227</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5759727012238772</v>
+        <v>1.382635252348718</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0057074316668778</v>
+        <v>0.0862430049296143</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6835</v>
+        <v>6754</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>127.4966129970479</v>
+        <v>157.3041461919019</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>30.95</v>
+        <v>42</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.86888458619469</v>
+        <v>46.91933887744142</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>19.41037629061972</v>
+        <v>12.8245984269191</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.348347797286834</v>
+        <v>1.503731132873442</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.1441550740909951</v>
+        <v>0.09212468026493301</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6790</v>
+        <v>6732</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>122.6837300244773</v>
+        <v>156.5099095303312</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>38.2</v>
+        <v>154</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>45.77112885349448</v>
+        <v>43.79887754734904</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>14.04817566001379</v>
+        <v>19.38344309739877</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.9379469133271756</v>
+        <v>0.7061578652792361</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0632224751026981</v>
+        <v>0.8198041431559577</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6684</v>
+        <v>6641</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>113.9717161419156</v>
+        <v>152.4127275977326</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>47</v>
+        <v>17.75</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>44.57152397927653</v>
+        <v>44.95897762909441</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>11.72207806770276</v>
+        <v>8.460812037148109</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.453873865565929</v>
+        <v>0.5759727012238772</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0778885826654611</v>
+        <v>0.0057074317145765</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6838</v>
+        <v>6684</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>110.4502010221674</v>
+        <v>113.9717161419156</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>44.00291036279714</v>
+        <v>44.57152405671072</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.4940876917252</v>
+        <v>11.72207812592502</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.3391458275212506</v>
+        <v>0.453873865565929</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0421844257028737</v>
+        <v>0.0778885823411159</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6504</v>
+        <v>6838</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>108.063746484693</v>
+        <v>110.4502010221674</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>49.99063802606414</v>
+        <v>44.0029108437478</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>17.33528651740714</v>
+        <v>11.49408786419172</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4147173476520469</v>
+        <v>0.3391458275212506</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.09089765873878659</v>
+        <v>0.0421844253022047</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>6556</v>
+        <v>6504</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>63.6685386074891</v>
+        <v>108.063746484693</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>61.4</v>
+        <v>38</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45.48900402135004</v>
+        <v>49.99063797753866</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.22481906925286</v>
+        <v>17.3352865071725</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.2268193064760106</v>
+        <v>0.4147173476520469</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.3918561346766518</v>
+        <v>-0.09089765875786431</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
